--- a/Data/Excel/world_building_level.xlsx
+++ b/Data/Excel/world_building_level.xlsx
@@ -218,10 +218,10 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>200101</v>
+        <v>30010001</v>
       </c>
       <c r="C5">
-        <v>2001</v>
+        <v>30000001</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -238,16 +238,16 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>200201</v>
+        <v>30010002</v>
       </c>
       <c r="C6">
-        <v>2002</v>
+        <v>30000002</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>200201</v>
+        <v>30901001</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -258,16 +258,16 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>200301</v>
+        <v>30010003</v>
       </c>
       <c r="C7">
-        <v>2003</v>
+        <v>30000003</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>200301</v>
+        <v>30901002</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -278,16 +278,16 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>200401</v>
+        <v>30010004</v>
       </c>
       <c r="C8">
-        <v>2004</v>
+        <v>30000004</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>200401</v>
+        <v>30901003</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -298,16 +298,16 @@
     </row>
     <row r="9">
       <c r="B9">
-        <v>200501</v>
+        <v>30010005</v>
       </c>
       <c r="C9">
-        <v>2005</v>
+        <v>30000005</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>200501</v>
+        <v>30901004</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -318,16 +318,16 @@
     </row>
     <row r="10">
       <c r="B10">
-        <v>200601</v>
+        <v>30010006</v>
       </c>
       <c r="C10">
-        <v>2006</v>
+        <v>30000006</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>200601</v>
+        <v>30901005</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -338,16 +338,16 @@
     </row>
     <row r="11">
       <c r="B11">
-        <v>200701</v>
+        <v>30010007</v>
       </c>
       <c r="C11">
-        <v>2007</v>
+        <v>30000007</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>200701</v>
+        <v>30901006</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -358,16 +358,16 @@
     </row>
     <row r="12">
       <c r="B12">
-        <v>201101</v>
+        <v>30010008</v>
       </c>
       <c r="C12">
-        <v>2011</v>
+        <v>30001001</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>201101</v>
+        <v>30901007</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -378,16 +378,16 @@
     </row>
     <row r="13">
       <c r="B13">
-        <v>201201</v>
+        <v>30010009</v>
       </c>
       <c r="C13">
-        <v>2012</v>
+        <v>30001002</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>201201</v>
+        <v>30901008</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -398,16 +398,16 @@
     </row>
     <row r="14">
       <c r="B14">
-        <v>201301</v>
+        <v>30010010</v>
       </c>
       <c r="C14">
-        <v>2013</v>
+        <v>30001003</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>201301</v>
+        <v>30901009</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -418,16 +418,16 @@
     </row>
     <row r="15">
       <c r="B15">
-        <v>202101</v>
+        <v>30010011</v>
       </c>
       <c r="C15">
-        <v>2021</v>
+        <v>30002001</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>202101</v>
+        <v>30901010</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -438,16 +438,16 @@
     </row>
     <row r="16">
       <c r="B16">
-        <v>202201</v>
+        <v>30010012</v>
       </c>
       <c r="C16">
-        <v>2022</v>
+        <v>30002002</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>202201</v>
+        <v>30901011</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -458,16 +458,16 @@
     </row>
     <row r="17">
       <c r="B17">
-        <v>202301</v>
+        <v>30010013</v>
       </c>
       <c r="C17">
-        <v>2023</v>
+        <v>30002003</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>202301</v>
+        <v>30901012</v>
       </c>
       <c r="F17">
         <v>0</v>

--- a/Data/Excel/world_building_level.xlsx
+++ b/Data/Excel/world_building_level.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -227,7 +227,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30901013</v>
       </c>
       <c r="F5">
         <v>0</v>
